--- a/cars.xlsx
+++ b/cars.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Plocha\2026.LUXES_EXECUTIVE_FINAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Plocha\2026.LUXES_EXECUTIVE_FINAL\LUXES_EXECUTIVE_AUTO_CSV_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA0A54D-BC57-4A43-B83A-D73B13FD1922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B767C1-8CC3-43AD-A11D-04D50D8F0068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>LUXES EXECUTIVE — БАЗА АВТОМОБИЛЕЙ</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Sloupec1</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz S 500.jpg</t>
+  </si>
+  <si>
+    <t>Maybach HUD</t>
   </si>
 </sst>
 </file>
@@ -207,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -221,10 +227,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -438,25 +447,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
     </row>
     <row r="2" spans="1:18" ht="21.95" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -597,7 +606,7 @@
       <c r="K4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>69900</v>
       </c>
       <c r="N4" t="s">
@@ -647,7 +656,7 @@
       <c r="K5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>139900</v>
       </c>
       <c r="N5" t="s">
@@ -663,24 +672,40 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" ht="28.5">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="4"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+      <c r="O6" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="2"/>
     </row>
